--- a/data/trans_dic/IP25A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,14 +519,13 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -535,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -573,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -629,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -646,62 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>45,16%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -714,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 31,02</t>
+          <t>21,76; 34,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 39,72</t>
+          <t>29,23; 42,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,28; 50,47</t>
+          <t>41,48; 56,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 18,04</t>
+          <t>22,65; 34,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,58; 31,15</t>
+          <t>28,88; 42,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,01; 39,66</t>
+          <t>44,18; 58,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 53,73</t>
+          <t>23,59; 32,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 19,88</t>
+          <t>31,32; 41,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,26; 29,5</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28,51; 37,64</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40,28; 50,12</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,12; 16,64</t>
+          <t>44,88; 55,5</t>
         </is>
       </c>
     </row>
@@ -786,62 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>31,39%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -854,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 42,43</t>
+          <t>36,32; 47,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 36,39</t>
+          <t>28,97; 39,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,02; 40,66</t>
+          <t>33,65; 44,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 17,32</t>
+          <t>33,54; 44,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 39,28</t>
+          <t>30,1; 41,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 37,07</t>
+          <t>35,18; 46,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,67; 42,85</t>
+          <t>36,25; 44,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,51</t>
+          <t>30,71; 38,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,61; 39,11</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>27,76; 34,65</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32,27; 39,71</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 15,7</t>
+          <t>36,19; 44,18</t>
         </is>
       </c>
     </row>
@@ -926,62 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>28,94%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40,57%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -994,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,15; 38,57</t>
+          <t>30,02; 43,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 32,35</t>
+          <t>25,07; 38,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,79; 48,6</t>
+          <t>40,14; 52,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 25,5</t>
+          <t>32,77; 46,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,53; 41,18</t>
+          <t>28,41; 41,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 36,74</t>
+          <t>35,01; 48,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,38; 44,61</t>
+          <t>33,85; 43,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 20,24</t>
+          <t>28,98; 37,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,7; 38,05</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>25,4; 33,5</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36,62; 45,31</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12,52; 21,17</t>
+          <t>39,14; 48,2</t>
         </is>
       </c>
     </row>
@@ -1066,62 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41,48%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -1134,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,92; 40,12</t>
+          <t>31,48; 43,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,71; 40,28</t>
+          <t>32,64; 44,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,96; 45,46</t>
+          <t>39,39; 52,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,17</t>
+          <t>37,86; 49,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,65; 43,57</t>
+          <t>33,12; 44,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,51; 41,47</t>
+          <t>43,31; 56,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,15; 48,9</t>
+          <t>36,1; 44,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,89</t>
+          <t>34,64; 43,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 40,06</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31,27; 39,46</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37,51; 45,57</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,5; 15,64</t>
+          <t>43,79; 52,47</t>
         </is>
       </c>
     </row>
@@ -1206,62 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1274,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,9; 35,54</t>
+          <t>33,28; 39,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,65; 34,63</t>
+          <t>32,47; 39,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,76; 42,71</t>
+          <t>41,56; 48,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,25</t>
+          <t>35,01; 41,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,65; 36,39</t>
+          <t>33,47; 39,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,91; 35,73</t>
+          <t>42,34; 48,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,47; 44,47</t>
+          <t>35,01; 39,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,14</t>
+          <t>33,91; 38,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,16; 35,08</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30,31; 34,21</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>38,1; 42,5</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,08; 15,71</t>
+          <t>42,89; 47,56</t>
         </is>
       </c>
     </row>
@@ -1342,15 +1171,966 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>35066</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46498</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57703</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50646</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69553</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73855</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>97144</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>127256</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>27310; 43338</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37528; 55191</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48653; 66601</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30902; 47632</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>40754; 60585</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>59490; 79389</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>61785; 85197</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>84413; 110740</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>113076; 139840</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>72011</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63985</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72661</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71837</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71031</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83906</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>143848</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>135016</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>156567</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>62642; 82058</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53901; 73764</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>62379; 82969</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>61513; 81989</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>60422; 82510</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>71805; 94932</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>129030; 156713</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>118797; 150235</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>140934; 172074</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>44505</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41270</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66182</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52455</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51908</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64728</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96960</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>93178</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>130909</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>36712; 53767</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32919; 50131</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57386; 75597</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43292; 61060</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>42414; 61234</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>54818; 75400</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>86119; 110742</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>81333; 106552</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>117240; 144394</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>71484</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82489</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>78389</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74644</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88876</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>149874</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>147289</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>171365</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>60894; 84351</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>60789; 83487</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69615; 92934</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68145; 88379</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>63556; 85691</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>77830; 101006</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>134814; 165135</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>130976; 163755</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>156104; 187027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>223065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>224398</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>279034</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>464536</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>472627</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>586097</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>204283; 241902</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>205233; 246614</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>258655; 300004</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>221272; 262514</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>228621; 267905</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>285822; 328199</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>436116; 490173</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>445925; 503374</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>556494; 617007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/IP25A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,76; 34,53</t>
+          <t>21,82; 34,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,23; 42,99</t>
+          <t>28,92; 43,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,48; 56,78</t>
+          <t>40,61; 56,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 34,91</t>
+          <t>22,35; 34,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,88; 42,93</t>
+          <t>28,95; 43,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,18; 58,96</t>
+          <t>44,36; 58,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,59; 32,53</t>
+          <t>24,11; 33,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,32; 41,09</t>
+          <t>31,2; 41,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,88; 55,5</t>
+          <t>45,31; 55,94</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,32; 47,57</t>
+          <t>35,79; 47,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,97; 39,65</t>
+          <t>29,1; 39,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,65; 44,76</t>
+          <t>34,34; 45,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,54; 44,7</t>
+          <t>33,58; 44,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,1; 41,1</t>
+          <t>29,95; 40,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,18; 46,51</t>
+          <t>35,82; 46,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,25; 44,03</t>
+          <t>35,93; 44,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,71; 38,84</t>
+          <t>30,96; 38,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,19; 44,18</t>
+          <t>36,33; 44,22</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,02; 43,96</t>
+          <t>29,69; 43,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,07; 38,17</t>
+          <t>25,21; 38,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,14; 52,87</t>
+          <t>40,35; 53,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 46,22</t>
+          <t>33,33; 46,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,41; 41,02</t>
+          <t>29,16; 42,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,01; 48,15</t>
+          <t>35,34; 48,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 43,53</t>
+          <t>33,74; 43,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,98; 37,97</t>
+          <t>29,44; 37,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,14; 48,2</t>
+          <t>39,14; 48,06</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,48; 43,6</t>
+          <t>31,01; 42,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,64; 44,83</t>
+          <t>32,67; 45,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,39; 52,58</t>
+          <t>39,84; 52,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,86; 49,1</t>
+          <t>37,93; 50,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,12; 44,66</t>
+          <t>33,19; 45,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,31; 56,2</t>
+          <t>43,53; 55,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 44,22</t>
+          <t>35,81; 44,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,64; 43,31</t>
+          <t>35,07; 43,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,79; 52,47</t>
+          <t>43,65; 52,89</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 39,41</t>
+          <t>33,1; 39,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,47; 39,02</t>
+          <t>32,37; 38,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,56; 48,2</t>
+          <t>41,77; 48,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,01; 41,54</t>
+          <t>34,95; 41,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,47; 39,22</t>
+          <t>33,46; 39,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,34; 48,62</t>
+          <t>42,2; 48,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,01; 39,35</t>
+          <t>35,17; 39,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,91; 38,28</t>
+          <t>33,72; 37,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,89; 47,56</t>
+          <t>43,1; 47,51</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27310; 43338</t>
+          <t>27378; 43789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37528; 55191</t>
+          <t>37124; 55720</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48653; 66601</t>
+          <t>47639; 66535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30902; 47632</t>
+          <t>30489; 47203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40754; 60585</t>
+          <t>40852; 60692</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59490; 79389</t>
+          <t>59723; 78797</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61785; 85197</t>
+          <t>63161; 87300</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84413; 110740</t>
+          <t>84075; 110781</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113076; 139840</t>
+          <t>114168; 140927</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62642; 82058</t>
+          <t>61728; 82266</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53901; 73764</t>
+          <t>54137; 74210</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62379; 82969</t>
+          <t>63645; 83495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61513; 81989</t>
+          <t>61589; 81989</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60422; 82510</t>
+          <t>60133; 81758</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71805; 94932</t>
+          <t>73114; 95158</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>129030; 156713</t>
+          <t>127887; 159776</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>118797; 150235</t>
+          <t>119768; 149908</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140934; 172074</t>
+          <t>141482; 172237</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36712; 53767</t>
+          <t>36316; 52805</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32919; 50131</t>
+          <t>33111; 49950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57386; 75597</t>
+          <t>57686; 77101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43292; 61060</t>
+          <t>44038; 61861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42414; 61234</t>
+          <t>43538; 62872</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54818; 75400</t>
+          <t>55342; 75654</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86119; 110742</t>
+          <t>85831; 109492</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81333; 106552</t>
+          <t>82611; 106520</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117240; 144394</t>
+          <t>117252; 143966</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60894; 84351</t>
+          <t>59988; 82504</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60789; 83487</t>
+          <t>60854; 83934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69615; 92934</t>
+          <t>70416; 92925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68145; 88379</t>
+          <t>68269; 90376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63556; 85691</t>
+          <t>63686; 86443</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77830; 101006</t>
+          <t>78242; 99555</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134814; 165135</t>
+          <t>133751; 166739</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130976; 163755</t>
+          <t>132607; 163235</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>156104; 187027</t>
+          <t>155581; 188535</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>204283; 241902</t>
+          <t>203162; 242286</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>205233; 246614</t>
+          <t>204560; 244649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>258655; 300004</t>
+          <t>259939; 298730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221272; 262514</t>
+          <t>220854; 261072</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>228621; 267905</t>
+          <t>228526; 269667</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285822; 328199</t>
+          <t>284906; 329572</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>436116; 490173</t>
+          <t>438107; 491761</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>445925; 503374</t>
+          <t>443391; 498740</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>556494; 617007</t>
+          <t>559183; 616350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>27,94%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>36,22%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>49,19%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 34,89</t>
+          <t>22,23; 34,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,92; 43,41</t>
+          <t>28,8; 42,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,61; 56,72</t>
+          <t>44,67; 59,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 34,6</t>
+          <t>21,31; 35,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,95; 43,01</t>
+          <t>29,35; 43,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,36; 58,52</t>
+          <t>41,09; 56,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,11; 33,33</t>
+          <t>24,3; 32,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,2; 41,11</t>
+          <t>31,32; 41,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,31; 55,94</t>
+          <t>44,99; 56,21</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>41,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>34,39%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>39,2%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,79; 47,69</t>
+          <t>33,43; 45,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 39,89</t>
+          <t>30,42; 41,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,34; 45,05</t>
+          <t>35,21; 46,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 44,7</t>
+          <t>36,03; 47,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,95; 40,72</t>
+          <t>28,96; 39,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,82; 46,62</t>
+          <t>33,22; 44,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,93; 44,89</t>
+          <t>36,49; 44,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 38,75</t>
+          <t>31,14; 39,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 44,22</t>
+          <t>36,0; 44,15</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>31,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>46,29%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 43,17</t>
+          <t>32,56; 46,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,21; 38,03</t>
+          <t>28,57; 40,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,35; 53,93</t>
+          <t>35,19; 47,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,33; 46,82</t>
+          <t>29,89; 43,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,16; 42,12</t>
+          <t>25,77; 38,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,34; 48,32</t>
+          <t>40,29; 53,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,74; 43,04</t>
+          <t>33,24; 42,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,44; 37,96</t>
+          <t>28,69; 37,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,14; 48,06</t>
+          <t>38,91; 48,31</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>36,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>39,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>46,67%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,01; 42,65</t>
+          <t>38,11; 49,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,67; 45,07</t>
+          <t>32,97; 45,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,84; 52,58</t>
+          <t>43,73; 55,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,93; 50,21</t>
+          <t>31,38; 43,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,19; 45,05</t>
+          <t>32,78; 45,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,53; 55,39</t>
+          <t>39,92; 53,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 44,65</t>
+          <t>36,49; 44,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,07; 43,17</t>
+          <t>34,99; 43,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,65; 52,89</t>
+          <t>43,57; 52,35</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,48</t>
+          <t>35,15; 41,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,37; 38,71</t>
+          <t>33,42; 39,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,77; 48,0</t>
+          <t>42,36; 48,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,95; 41,31</t>
+          <t>33,18; 39,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,46; 39,48</t>
+          <t>32,33; 39,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,2; 48,82</t>
+          <t>41,9; 48,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,17; 39,48</t>
+          <t>35,16; 39,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,72; 37,93</t>
+          <t>33,89; 38,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 47,51</t>
+          <t>43,07; 47,32</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>80</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50646</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69553</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>35066</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>46498</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>57703</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50646</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69553</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27378; 43789</t>
+          <t>30329; 46985</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37124; 55720</t>
+          <t>40644; 60225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47639; 66535</t>
+          <t>60149; 80162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30489; 47203</t>
+          <t>26749; 44112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40852; 60692</t>
+          <t>37673; 55582</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59723; 78797</t>
+          <t>48204; 66677</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63161; 87300</t>
+          <t>63653; 86407</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84075; 110781</t>
+          <t>84396; 111132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114168; 140927</t>
+          <t>113342; 141626</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>118</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71837</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71031</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>72011</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>63985</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>72661</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71837</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71031</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83906</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61728; 82266</t>
+          <t>61322; 83038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54137; 74210</t>
+          <t>61083; 82729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63645; 83495</t>
+          <t>71863; 94690</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61589; 81989</t>
+          <t>62143; 82769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60133; 81758</t>
+          <t>53878; 73762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73114; 95158</t>
+          <t>61580; 83273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127887; 159776</t>
+          <t>129880; 159230</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>119768; 149908</t>
+          <t>120445; 151188</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>141482; 172237</t>
+          <t>140212; 171931</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52455</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51908</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64728</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>44505</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>41270</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>66182</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52455</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>51908</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64728</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36316; 52805</t>
+          <t>43018; 61390</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33111; 49950</t>
+          <t>42658; 61159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57686; 77101</t>
+          <t>55105; 74737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44038; 61861</t>
+          <t>36561; 52976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43538; 62872</t>
+          <t>33844; 50051</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55342; 75654</t>
+          <t>57600; 76575</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85831; 109492</t>
+          <t>84581; 108276</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82611; 106520</t>
+          <t>80513; 105945</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117252; 143966</t>
+          <t>116567; 144714</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>78389</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74644</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88876</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>71484</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>72645</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>82489</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78389</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>74644</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88876</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59988; 82504</t>
+          <t>68595; 88895</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60854; 83934</t>
+          <t>63268; 87372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70416; 92925</t>
+          <t>78591; 99485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68269; 90376</t>
+          <t>60711; 83314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63686; 86443</t>
+          <t>61043; 84989</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78242; 99555</t>
+          <t>70550; 93720</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>133751; 166739</t>
+          <t>136280; 165728</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>132607; 163235</t>
+          <t>132322; 164048</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>155581; 188535</t>
+          <t>155324; 186624</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>412</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>279034</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>203162; 242286</t>
+          <t>222136; 262108</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204560; 244649</t>
+          <t>228270; 270779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>259939; 298730</t>
+          <t>285940; 329699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220854; 261072</t>
+          <t>203647; 241490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>228526; 269667</t>
+          <t>204349; 246544</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>284906; 329572</t>
+          <t>260763; 300181</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>438107; 491761</t>
+          <t>438009; 492547</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>443391; 498740</t>
+          <t>445637; 501424</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>559183; 616350</t>
+          <t>558745; 613965</t>
         </is>
       </c>
     </row>
